--- a/invalid_hhids.xlsx
+++ b/invalid_hhids.xlsx
@@ -1282,82 +1282,82 @@
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="A109" s="2" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="2" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+      <c r="A112" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="2" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="2" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="2" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+      <c r="A118" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="2" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="2" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
+      <c r="A123" s="2" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="2" t="s">
         <v>123</v>
       </c>
     </row>
